--- a/Results_experiment/exp_4/eval_cycle_XI.xlsx
+++ b/Results_experiment/exp_4/eval_cycle_XI.xlsx
@@ -447,13 +447,13 @@
         <v>534</v>
       </c>
       <c r="D2">
-        <v>0.1217568147793546</v>
+        <v>0.2530058192576026</v>
       </c>
       <c r="E2">
-        <v>6.258244947355402</v>
+        <v>5.771700306503852</v>
       </c>
       <c r="F2">
-        <v>4.156586728194791</v>
+        <v>4.062810977202341</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>521</v>
       </c>
       <c r="D3">
-        <v>0.5505073898840032</v>
+        <v>0.5439381882384604</v>
       </c>
       <c r="E3">
-        <v>4.039502509319011</v>
+        <v>4.068913508461166</v>
       </c>
       <c r="F3">
-        <v>2.496208262692372</v>
+        <v>2.473183357255129</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>429</v>
       </c>
       <c r="D4">
-        <v>0.2652804125773056</v>
+        <v>0.3611091535592282</v>
       </c>
       <c r="E4">
-        <v>6.671566550515742</v>
+        <v>6.221288572951382</v>
       </c>
       <c r="F4">
-        <v>4.112225764698082</v>
+        <v>3.841294802846886</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>374</v>
       </c>
       <c r="D5">
-        <v>0.4394763742228369</v>
+        <v>0.3859051435987618</v>
       </c>
       <c r="E5">
-        <v>3.449191402223048</v>
+        <v>3.610256540611627</v>
       </c>
       <c r="F5">
-        <v>2.445717850510768</v>
+        <v>2.478792244140158</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>251</v>
       </c>
       <c r="D6">
-        <v>0.2774771527085945</v>
+        <v>0.05842512454655446</v>
       </c>
       <c r="E6">
-        <v>4.034972757147589</v>
+        <v>4.606194211616637</v>
       </c>
       <c r="F6">
-        <v>2.686715569451036</v>
+        <v>3.222747478174024</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>237</v>
       </c>
       <c r="D7">
-        <v>-0.441811864523145</v>
+        <v>-0.2612859271353813</v>
       </c>
       <c r="E7">
-        <v>5.927609923756608</v>
+        <v>5.544113262059573</v>
       </c>
       <c r="F7">
-        <v>3.746774148243138</v>
+        <v>3.339456100912788</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>223</v>
       </c>
       <c r="D8">
-        <v>0.3508105102078106</v>
+        <v>0.4711683473921705</v>
       </c>
       <c r="E8">
-        <v>3.134278924223527</v>
+        <v>2.8288545822674</v>
       </c>
       <c r="F8">
-        <v>2.480510278433695</v>
+        <v>2.120157162470935</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>84</v>
       </c>
       <c r="D9">
-        <v>-1.127968055061955</v>
+        <v>0.3999866296477522</v>
       </c>
       <c r="E9">
-        <v>14.17631885607319</v>
+        <v>7.527684087519727</v>
       </c>
       <c r="F9">
-        <v>8.177913263794922</v>
+        <v>4.655014791304157</v>
       </c>
     </row>
   </sheetData>
